--- a/gte/nodes/P/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
+++ b/gte/nodes/P/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>33.348036823434143</v>
+        <v>41.489338481118047</v>
       </c>
       <c r="B1">
-        <v>49.700225358397255</v>
+        <v>43.078081432625218</v>
       </c>
       <c r="C1">
         <v>338.08353538342624</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>30.750172861255336</v>
+        <v>38.71071144614735</v>
       </c>
       <c r="B2">
-        <v>47.978833961822318</v>
+        <v>41.734108634456376</v>
       </c>
       <c r="C2">
         <v>338.08353538342624</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>28.198702638791453</v>
+        <v>35.965762878690889</v>
       </c>
       <c r="B3">
-        <v>46.219368292455712</v>
+        <v>40.351399183973193</v>
       </c>
       <c r="C3">
         <v>338.08353538342624</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>25.686187690548564</v>
+        <v>33.249750761390793</v>
       </c>
       <c r="B4">
-        <v>44.427932927468973</v>
+        <v>38.935407304340167</v>
       </c>
       <c r="C4">
         <v>338.08353538342624</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>23.205189551032777</v>
+        <v>30.557933076889203</v>
       </c>
       <c r="B5">
-        <v>42.610632444033669</v>
+        <v>37.491587218721762</v>
       </c>
       <c r="C5">
         <v>338.08353538342624</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>20.751355650460603</v>
+        <v>27.88753235901617</v>
       </c>
       <c r="B6">
-        <v>40.771038895842793</v>
+        <v>36.023133542232067</v>
       </c>
       <c r="C6">
         <v>338.08353538342624</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>18.332677001890257</v>
+        <v>25.243629346353469</v>
       </c>
       <c r="B7">
-        <v>38.9025942426752</v>
+        <v>34.524202457783495</v>
       </c>
       <c r="C7">
         <v>338.08353538342624</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>15.957586363246769</v>
+        <v>22.631586168849008</v>
       </c>
       <c r="B8">
-        <v>36.998377914479917</v>
+        <v>32.988626494621421</v>
       </c>
       <c r="C8">
         <v>338.08353538342624</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>13.623939889080546</v>
+        <v>20.050032317163414</v>
       </c>
       <c r="B9">
-        <v>35.060149315801</v>
+        <v>31.417981999524386</v>
       </c>
       <c r="C9">
         <v>338.08353538342624</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>11.327703379996066</v>
+        <v>17.496394185681204</v>
       </c>
       <c r="B10">
-        <v>33.091219221092636</v>
+        <v>29.815229109139882</v>
       </c>
       <c r="C10">
         <v>338.08353538342624</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>9.06785782418847</v>
+        <v>14.97001842296976</v>
       </c>
       <c r="B11">
-        <v>31.092423909854457</v>
+        <v>28.181119302058033</v>
       </c>
       <c r="C11">
         <v>338.08353538342624</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>6.8441380067506081</v>
+        <v>12.470731741142153</v>
       </c>
       <c r="B12">
-        <v>29.063981037847476</v>
+        <v>26.515851892354615</v>
       </c>
       <c r="C12">
         <v>338.08353538342624</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>4.6562787127753174</v>
+        <v>9.9983608523114746</v>
       </c>
       <c r="B13">
-        <v>27.006108260832711</v>
+        <v>24.819626194105396</v>
       </c>
       <c r="C13">
         <v>338.08353538342624</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2.504012764689048</v>
+        <v>7.5527315075441024</v>
       </c>
       <c r="B14">
-        <v>24.919024845286227</v>
+        <v>23.092642626772879</v>
       </c>
       <c r="C14">
         <v>338.08353538342624</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>0.38706513425272249</v>
+        <v>5.133665613719689</v>
       </c>
       <c r="B15">
-        <v>22.802956500544333</v>
+        <v>21.335106031366532</v>
       </c>
       <c r="C15">
         <v>338.08353538342624</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.6948411694391232</v>
+        <v>2.7409841166711848</v>
       </c>
       <c r="B16">
-        <v>20.658130546658402</v>
+        <v>19.547222354282571</v>
       </c>
       <c r="C16">
         <v>338.08353538342624</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.7419831372919461</v>
+        <v>0.37450796223154231</v>
       </c>
       <c r="B17">
-        <v>18.484774303679817</v>
+        <v>17.729197541917181</v>
       </c>
       <c r="C17">
         <v>338.08353538342624</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-5.75454523404356</v>
+        <v>-1.9658827032504938</v>
       </c>
       <c r="B18">
-        <v>16.283039157566897</v>
+        <v>15.881169448797611</v>
       </c>
       <c r="C18">
         <v>338.08353538342624</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.7323418197611495</v>
+        <v>-4.2800709313630305</v>
       </c>
       <c r="B19">
-        <v>14.052772757905883</v>
+        <v>14.003003561975266</v>
       </c>
       <c r="C19">
         <v>338.08353538342624</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-9.6750947283442734</v>
+        <v>-6.5678805731784244</v>
       </c>
       <c r="B20">
-        <v>11.793746820189934</v>
+        <v>12.094497276632568</v>
       </c>
       <c r="C20">
         <v>338.08353538342624</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-11.582525793692456</v>
+        <v>-8.8291354797689827</v>
       </c>
       <c r="B21">
-        <v>9.505733059912254</v>
+        <v>10.155447987951966</v>
       </c>
       <c r="C21">
         <v>338.08353538342624</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-13.454449571738749</v>
+        <v>-11.063718218516286</v>
       </c>
       <c r="B22">
-        <v>7.1885792874016126</v>
+        <v>8.1857206260550655</v>
       </c>
       <c r="C22">
         <v>338.08353538342624</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-15.291051506550105</v>
+        <v>-13.271746222038754</v>
       </c>
       <c r="B23">
-        <v>4.842437692329236</v>
+        <v>6.1854502608202573</v>
       </c>
       <c r="C23">
         <v>338.08353538342624</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-17.092609764226982</v>
+        <v>-15.453395639264071</v>
       </c>
       <c r="B24">
-        <v>2.4675365592019323</v>
+        <v>4.1548394970651028</v>
       </c>
       <c r="C24">
         <v>338.08353538342624</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-18.859402510869852</v>
+        <v>-17.6088426191199</v>
       </c>
       <c r="B25">
-        <v>0.064104172526526643</v>
+        <v>2.0940909396071663</v>
       </c>
       <c r="C25">
         <v>338.08353538342624</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-20.5916153864115</v>
+        <v>-19.738204110018113</v>
       </c>
       <c r="B26">
-        <v>-2.367707117283206</v>
+        <v>0.0033391013950518494</v>
       </c>
       <c r="C26">
         <v>338.08353538342624</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-22.289063926114128</v>
+        <v>-21.841360258307471</v>
       </c>
       <c r="B27">
-        <v>-4.8280486961855988</v>
+        <v>-2.117553872098485</v>
       </c>
       <c r="C27">
         <v>338.08353538342624</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-23.951471139072275</v>
+        <v>-23.918132009820916</v>
       </c>
       <c r="B28">
-        <v>-7.317147884232031</v>
+        <v>-4.2687939272696447</v>
       </c>
       <c r="C28">
         <v>338.08353538342624</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-25.57856003438048</v>
+        <v>-25.968340310391408</v>
       </c>
       <c r="B29">
-        <v>-9.8352320014738677</v>
+        <v>-6.4505870105146332</v>
       </c>
       <c r="C29">
         <v>338.08353538342624</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-27.170055583799666</v>
+        <v>-27.991807066898584</v>
       </c>
       <c r="B30">
-        <v>-12.382526757247423</v>
+        <v>-8.6631379628429137</v>
       </c>
       <c r="C30">
         <v>338.08353538342624</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-28.725690609756285</v>
+        <v>-29.988358030408843</v>
       </c>
       <c r="B31">
-        <v>-14.959251418028764</v>
+        <v>-10.906647203717</v>
       </c>
       <c r="C31">
         <v>338.08353538342624</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-30.245199897343173</v>
+        <v>-31.957819913035259</v>
       </c>
       <c r="B32">
-        <v>-17.565623639578906</v>
+        <v>-13.181314047212657</v>
       </c>
       <c r="C32">
         <v>338.08353538342624</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-31.728318231653159</v>
+        <v>-33.900019426890914</v>
       </c>
       <c r="B33">
-        <v>-20.201861077658865</v>
+        <v>-15.487337807405663</v>
       </c>
       <c r="C33">
         <v>338.08353538342624</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-33.174026600881412</v>
+        <v>-35.814303220543174</v>
       </c>
       <c r="B34">
-        <v>-22.868800011768272</v>
+        <v>-17.825469962886121</v>
       </c>
       <c r="C34">
         <v>338.08353538342624</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-34.5782908056324</v>
+        <v>-37.698097688376578</v>
       </c>
       <c r="B35">
-        <v>-25.569751216361325</v>
+        <v>-20.198670650301562</v>
       </c>
       <c r="C35">
         <v>338.08353538342624</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-35.938967000456529</v>
+        <v>-39.550032321051731</v>
       </c>
       <c r="B36">
-        <v>-28.306474095982033</v>
+        <v>-22.608516216430491</v>
       </c>
       <c r="C36">
         <v>338.08353538342624</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-37.26448794327883</v>
+        <v>-41.375469248516552</v>
       </c>
       <c r="B37">
-        <v>-31.072048080579481</v>
+        <v>-25.048839190518287</v>
       </c>
       <c r="C37">
         <v>338.08353538342624</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-38.562844647157512</v>
+        <v>-43.17948920935283</v>
       </c>
       <c r="B38">
-        <v>-33.8599151299325</v>
+        <v>-27.513795755477389</v>
       </c>
       <c r="C38">
         <v>338.08353538342624</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-39.82968454230911</v>
+        <v>-44.959314737390592</v>
       </c>
       <c r="B39">
-        <v>-36.6736472977341</v>
+        <v>-30.006580526421871</v>
       </c>
       <c r="C39">
         <v>338.08353538342624</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-41.057569163239691</v>
+        <v>-46.710203815271996</v>
       </c>
       <c r="B40">
-        <v>-39.519349161155809</v>
+        <v>-32.5326477265162</v>
       </c>
       <c r="C40">
         <v>338.08353538342624</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-42.239060044455357</v>
+        <v>-48.427414425639142</v>
       </c>
       <c r="B41">
-        <v>-42.403125297369179</v>
+        <v>-35.097451578924847</v>
       </c>
       <c r="C41">
         <v>338.08353538342624</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-41.9074879820946</v>
+        <v>-48.216340486507953</v>
       </c>
       <c r="B42">
-        <v>-42.675238846093578</v>
+        <v>-35.340226811773093</v>
       </c>
       <c r="C42">
         <v>338.08353538342624</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-40.388121914348176</v>
+        <v>-46.284043460090061</v>
       </c>
       <c r="B43">
-        <v>-40.068749087321656</v>
+        <v>-33.022813304918955</v>
       </c>
       <c r="C43">
         <v>338.08353538342624</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-38.857073159384221</v>
+        <v>-44.340164515939122</v>
       </c>
       <c r="B44">
-        <v>-37.471847040659007</v>
+        <v>-30.718721209443384</v>
       </c>
       <c r="C44">
         <v>338.08353538342624</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-37.307331867343514</v>
+        <v>-42.380248084578717</v>
       </c>
       <c r="B45">
-        <v>-34.89028552830554</v>
+        <v>-28.433075278888055</v>
       </c>
       <c r="C45">
         <v>338.08353538342624</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-35.731888188366874</v>
+        <v>-40.399838596532412</v>
       </c>
       <c r="B46">
-        <v>-32.329817372461164</v>
+        <v>-26.171000266794614</v>
       </c>
       <c r="C46">
         <v>338.08353538342624</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-34.126805390678754</v>
+        <v>-38.396436669491877</v>
       </c>
       <c r="B47">
-        <v>-29.793673358150976</v>
+        <v>-23.935370938870204</v>
       </c>
       <c r="C47">
         <v>338.08353538342624</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-32.500439214838309</v>
+        <v>-36.375367669821152</v>
       </c>
       <c r="B48">
-        <v>-27.274996121700912</v>
+        <v>-21.720062109483891</v>
       </c>
       <c r="C48">
         <v>338.08353538342624</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-30.861568318793303</v>
+        <v>-34.34222600389937</v>
       </c>
       <c r="B49">
-        <v>-24.7665812208844</v>
+        <v>-19.518639145743769</v>
       </c>
       <c r="C49">
         <v>338.08353538342624</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-29.208370557711387</v>
+        <v>-32.295857489493905</v>
       </c>
       <c r="B50">
-        <v>-22.26992404796432</v>
+        <v>-17.33242957705232</v>
       </c>
       <c r="C50">
         <v>338.08353538342624</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-27.537113286367585</v>
+        <v>-30.233891472209276</v>
       </c>
       <c r="B51">
-        <v>-19.788087898837979</v>
+        <v>-15.164160107498285</v>
       </c>
       <c r="C51">
         <v>338.08353538342624</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-25.847022660746642</v>
+        <v>-28.155839997610723</v>
       </c>
       <c r="B52">
-        <v>-17.3217078494513</v>
+        <v>-13.014391977621397</v>
       </c>
       <c r="C52">
         <v>338.08353538342624</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-24.138064537135762</v>
+        <v>-26.061685786253634</v>
       </c>
       <c r="B53">
-        <v>-14.870811920762371</v>
+        <v>-10.883145062074139</v>
       </c>
       <c r="C53">
         <v>338.08353538342624</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-22.410204771822116</v>
+        <v>-23.951411558693415</v>
       </c>
       <c r="B54">
-        <v>-12.435428133729266</v>
+        <v>-8.7704392355089666</v>
       </c>
       <c r="C54">
         <v>338.08353538342624</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-20.663390953753844</v>
+        <v>-21.824988118405731</v>
       </c>
       <c r="B55">
-        <v>-10.015599500894165</v>
+        <v>-6.6763080794898872</v>
       </c>
       <c r="C55">
         <v>338.08353538342624</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-18.897497602522794</v>
+        <v>-19.682338600547272</v>
       </c>
       <c r="B56">
-        <v>-7.6114290011356678</v>
+        <v>-4.6008400032269963</v>
       </c>
       <c r="C56">
         <v>338.08353538342624</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-17.11238097038175</v>
+        <v>-17.523374223195</v>
       </c>
       <c r="B57">
-        <v>-5.2230346049164771</v>
+        <v>-2.5441371228419087</v>
       </c>
       <c r="C57">
         <v>338.08353538342624</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-15.307897309583497</v>
+        <v>-15.34800620442587</v>
       </c>
       <c r="B58">
-        <v>-2.850534282699293</v>
+        <v>-0.50630155445625324</v>
       </c>
       <c r="C58">
         <v>338.08353538342624</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-13.483980596483754</v>
+        <v>-13.156194940640319</v>
       </c>
       <c r="B59">
-        <v>-0.49398221856710933</v>
+        <v>1.5126211502472553</v>
       </c>
       <c r="C59">
         <v>338.08353538342624</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-11.640875703849972</v>
+        <v>-10.948097541532691</v>
       </c>
       <c r="B60">
-        <v>1.8468225489159142</v>
+        <v>3.5128116973414887</v>
       </c>
       <c r="C60">
         <v>338.08353538342624</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-9.778905228552528</v>
+        <v>-8.7239202951208057</v>
       </c>
       <c r="B61">
-        <v>4.1721447675653236</v>
+        <v>5.4945073573382279</v>
       </c>
       <c r="C61">
         <v>338.08353538342624</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-7.8983917674617983</v>
+        <v>-6.4838694894224824</v>
       </c>
       <c r="B62">
-        <v>6.4822491851966717</v>
+        <v>7.45794540074925</v>
       </c>
       <c r="C62">
         <v>338.08353538342624</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.9995503851580541</v>
+        <v>-4.2280826497829471</v>
       </c>
       <c r="B63">
-        <v>8.7773123003536462</v>
+        <v>9.40328400791573</v>
       </c>
       <c r="C63">
         <v>338.08353538342624</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.0821660170610174</v>
+        <v>-1.9564222508569673</v>
       </c>
       <c r="B64">
-        <v>11.057157614492562</v>
+        <v>11.330364998496497</v>
       </c>
       <c r="C64">
         <v>338.08353538342624</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.145916066300332</v>
+        <v>0.33131799537325973</v>
       </c>
       <c r="B65">
-        <v>13.321520379797857</v>
+        <v>13.238951101979763</v>
       </c>
       <c r="C65">
         <v>338.08353538342624</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.19047793600559387</v>
+        <v>2.6353443769255729</v>
       </c>
       <c r="B66">
-        <v>15.570135848453997</v>
+        <v>15.128805047853762</v>
       </c>
       <c r="C66">
         <v>338.08353538342624</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1.7843932465906285</v>
+        <v>4.9558140034943037</v>
       </c>
       <c r="B67">
-        <v>17.802803059025134</v>
+        <v>16.999746130045608</v>
       </c>
       <c r="C67">
         <v>338.08353538342624</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3.7786314578440572</v>
+        <v>7.2926872714798918</v>
       </c>
       <c r="B68">
-        <v>20.019576195594265</v>
+        <v>18.851819900238024</v>
       </c>
       <c r="C68">
         <v>338.08353538342624</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5.79209295000748</v>
+        <v>9.64587539895929</v>
       </c>
       <c r="B69">
-        <v>22.220573228624094</v>
+        <v>20.685128474552638</v>
       </c>
       <c r="C69">
         <v>338.08353538342624</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7.8246339753336827</v>
+        <v>12.015289604009466</v>
       </c>
       <c r="B70">
-        <v>24.40591212857731</v>
+        <v>22.499773969111057</v>
       </c>
       <c r="C70">
         <v>338.08353538342624</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>9.8761290534145161</v>
+        <v>14.400853021787105</v>
       </c>
       <c r="B71">
-        <v>26.575695874332528</v>
+        <v>24.295844793123393</v>
       </c>
       <c r="C71">
         <v>338.08353538342624</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>11.946525773198109</v>
+        <v>16.802536455767882</v>
       </c>
       <c r="B72">
-        <v>28.72996747843192</v>
+        <v>26.073374528153632</v>
       </c>
       <c r="C72">
         <v>338.08353538342624</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>14.035789990971651</v>
+        <v>19.220322626507183</v>
       </c>
       <c r="B73">
-        <v>30.86875496183357</v>
+        <v>27.832383048854258</v>
       </c>
       <c r="C73">
         <v>338.08353538342624</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>16.143887563022318</v>
+        <v>21.654194254560419</v>
       </c>
       <c r="B74">
-        <v>32.992086345495544</v>
+        <v>29.572890229877725</v>
       </c>
       <c r="C74">
         <v>338.08353538342624</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>18.270044645334874</v>
+        <v>24.103663385492808</v>
       </c>
       <c r="B75">
-        <v>35.100596705363785</v>
+        <v>31.295457311763773</v>
       </c>
       <c r="C75">
         <v>338.08353538342624</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>20.410528592684351</v>
+        <v>26.566359364908898</v>
       </c>
       <c r="B76">
-        <v>37.197349337335609</v>
+        <v>33.00281099860117</v>
       </c>
       <c r="C76">
         <v>338.08353538342624</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>22.563517260238378</v>
+        <v>29.041128010576024</v>
       </c>
       <c r="B77">
-        <v>39.28383963367385</v>
+        <v>34.69627881979234</v>
       </c>
       <c r="C77">
         <v>338.08353538342624</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>24.73778930594473</v>
+        <v>31.53356372887335</v>
       </c>
       <c r="B78">
-        <v>41.352863152151983</v>
+        <v>36.369426142445434</v>
       </c>
       <c r="C78">
         <v>338.08353538342624</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>26.941700470362562</v>
+        <v>34.048991886164906</v>
       </c>
       <c r="B79">
-        <v>43.397562529095929</v>
+        <v>38.016127780929509</v>
       </c>
       <c r="C79">
         <v>338.08353538342624</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>29.171314021716345</v>
+        <v>36.584913100142373</v>
       </c>
       <c r="B80">
-        <v>45.42116854953079</v>
+        <v>39.639258500951676</v>
       </c>
       <c r="C80">
         <v>338.08353538342624</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>31.419620110146859</v>
+        <v>39.136871801329285</v>
       </c>
       <c r="B81">
-        <v>47.42943403565647</v>
+        <v>41.243943056053624</v>
       </c>
       <c r="C81">
         <v>338.08353538342624</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>33.679608885794906</v>
+        <v>41.700412420249236</v>
       </c>
       <c r="B82">
-        <v>49.428111809672863</v>
+        <v>42.835306199776973</v>
       </c>
       <c r="C82">
         <v>338.08353538342624</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>42.793815026186707</v>
+        <v>40.786431333828588</v>
       </c>
       <c r="B1">
-        <v>42.585979234405343</v>
+        <v>44.671676492532484</v>
       </c>
       <c r="C1">
         <v>592.998505179033</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>38.918358653682276</v>
+        <v>36.973540613589115</v>
       </c>
       <c r="B2">
-        <v>41.990804908034136</v>
+        <v>43.926640471788112</v>
       </c>
       <c r="C2">
         <v>592.998505179033</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>35.660684654794352</v>
+        <v>33.700890488137986</v>
       </c>
       <c r="B3">
-        <v>40.673044170784173</v>
+        <v>42.581395519969291</v>
       </c>
       <c r="C3">
         <v>592.998505179033</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>32.506177087726812</v>
+        <v>30.52685438127617</v>
       </c>
       <c r="B4">
-        <v>39.234615274525652</v>
+        <v>41.1265900959138</v>
       </c>
       <c r="C4">
         <v>592.998505179033</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>29.426166322560913</v>
+        <v>27.426713804840215</v>
       </c>
       <c r="B5">
-        <v>37.709051524624506</v>
+        <v>39.589686514563283</v>
       </c>
       <c r="C5">
         <v>592.998505179033</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>26.408927132834091</v>
+        <v>24.390295261547497</v>
       </c>
       <c r="B6">
-        <v>36.110067280162788</v>
+        <v>37.981987562098929</v>
       </c>
       <c r="C6">
         <v>592.998505179033</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>23.447744758239594</v>
+        <v>21.411733995517253</v>
       </c>
       <c r="B7">
-        <v>34.445516430725533</v>
+        <v>36.310009000002168</v>
       </c>
       <c r="C7">
         <v>592.998505179033</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>20.538649629890383</v>
+        <v>18.487525354173293</v>
       </c>
       <c r="B8">
-        <v>32.72004196494003</v>
+        <v>34.577644507860981</v>
       </c>
       <c r="C8">
         <v>592.998505179033</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>17.675473478759919</v>
+        <v>15.612289138279689</v>
       </c>
       <c r="B9">
-        <v>30.940858571291329</v>
+        <v>32.790871503262132</v>
       </c>
       <c r="C9">
         <v>592.998505179033</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>14.851563490913712</v>
+        <v>12.780234562593195</v>
       </c>
       <c r="B10">
-        <v>29.115747684065141</v>
+        <v>30.956123566085495</v>
       </c>
       <c r="C10">
         <v>592.998505179033</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>12.060527372924746</v>
+        <v>9.9858040445011653</v>
       </c>
       <c r="B11">
-        <v>27.252186020892115</v>
+        <v>29.079575187384659</v>
       </c>
       <c r="C11">
         <v>592.998505179033</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.2989356660966251</v>
+        <v>7.2259865603780877</v>
       </c>
       <c r="B12">
-        <v>25.35418483291264</v>
+        <v>27.164571623493796</v>
       </c>
       <c r="C12">
         <v>592.998505179033</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>6.5749497301479893</v>
+        <v>4.507724119916559</v>
       </c>
       <c r="B13">
-        <v>23.412198221961209</v>
+        <v>25.203400280695789</v>
       </c>
       <c r="C13">
         <v>592.998505179033</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3.8934394541651502</v>
+        <v>1.8351395893569569</v>
       </c>
       <c r="B14">
-        <v>21.420530143886154</v>
+        <v>23.191480642156183</v>
       </c>
       <c r="C14">
         <v>592.998505179033</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>1.2345180262899098</v>
+        <v>-0.80887377218733481</v>
       </c>
       <c r="B15">
-        <v>19.402441119897063</v>
+        <v>21.147818348622359</v>
       </c>
       <c r="C15">
         <v>592.998505179033</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.4200545778545468</v>
+        <v>-3.4400059515519321</v>
       </c>
       <c r="B16">
-        <v>17.379265513536321</v>
+        <v>19.089845022815833</v>
       </c>
       <c r="C16">
         <v>592.998505179033</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-4.0571745317752512</v>
+        <v>-6.0470503122417059</v>
       </c>
       <c r="B17">
-        <v>15.335676492316093</v>
+        <v>17.005110057772626</v>
       </c>
       <c r="C17">
         <v>592.998505179033</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-6.65991127858452</v>
+        <v>-8.6155121767996476</v>
       </c>
       <c r="B18">
-        <v>13.251871305529798</v>
+        <v>14.877509823097935</v>
       </c>
       <c r="C18">
         <v>592.998505179033</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-9.2273711906856821</v>
+        <v>-11.144641327252058</v>
       </c>
       <c r="B19">
-        <v>11.126804725625956</v>
+        <v>12.706210824359109</v>
       </c>
       <c r="C19">
         <v>592.998505179033</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-11.76266987280485</v>
+        <v>-13.637123660496117</v>
       </c>
       <c r="B20">
-        <v>8.9641209058418241</v>
+        <v>10.494197101113999</v>
       </c>
       <c r="C20">
         <v>592.998505179033</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-14.26892292966811</v>
+        <v>-16.09564507342894</v>
       </c>
       <c r="B21">
-        <v>6.7674639994147059</v>
+        <v>8.2444526929204844</v>
       </c>
       <c r="C21">
         <v>592.998505179033</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-16.748690130388034</v>
+        <v>-18.522410361596904</v>
       </c>
       <c r="B22">
-        <v>4.5398280289239157</v>
+        <v>5.9594271342838727</v>
       </c>
       <c r="C22">
         <v>592.998505179033</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-19.202307901623016</v>
+        <v>-20.917699915143046</v>
       </c>
       <c r="B23">
-        <v>2.2816064943170287</v>
+        <v>3.6394319394992496</v>
       </c>
       <c r="C23">
         <v>592.998505179033</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-21.629556834417947</v>
+        <v>-23.281313022859653</v>
       </c>
       <c r="B24">
-        <v>-0.00745723511634544</v>
+        <v>1.2842441178091257</v>
       </c>
       <c r="C24">
         <v>592.998505179033</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-24.030217519817686</v>
+        <v>-25.613048973538973</v>
       </c>
       <c r="B25">
-        <v>-2.327619790086584</v>
+        <v>-1.1063593215439731</v>
       </c>
       <c r="C25">
         <v>592.998505179033</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-26.403976711360492</v>
+        <v>-27.912622394783931</v>
       </c>
       <c r="B26">
-        <v>-4.6792475579270914</v>
+        <v>-3.5326954281543372</v>
       </c>
       <c r="C26">
         <v>592.998505179033</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-28.750145812558241</v>
+        <v>-30.179409269440143</v>
       </c>
       <c r="B27">
-        <v>-7.0631459524634481</v>
+        <v>-5.9954574869635762</v>
       </c>
       <c r="C27">
         <v>592.998505179033</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-31.06794238941621</v>
+        <v>-32.4127009191639</v>
       </c>
       <c r="B28">
-        <v>-9.4802301441442722</v>
+        <v>-8.49543284175012</v>
       </c>
       <c r="C28">
         <v>592.998505179033</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-33.356584007939659</v>
+        <v>-34.611788665611485</v>
       </c>
       <c r="B29">
-        <v>-11.931415303418165</v>
+        <v>-11.033408836292383</v>
       </c>
       <c r="C29">
         <v>592.998505179033</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-35.615697460292388</v>
+        <v>-36.776310502461477</v>
       </c>
       <c r="B30">
-        <v>-14.41713795117397</v>
+        <v>-13.609787660705862</v>
       </c>
       <c r="C30">
         <v>592.998505179033</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-37.8465464432725</v>
+        <v>-38.907291111481683</v>
       </c>
       <c r="B31">
-        <v>-16.935920010061555</v>
+        <v>-16.22343089045437</v>
       </c>
       <c r="C31">
         <v>592.998505179033</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-40.050803879836629</v>
+        <v>-41.006101846462229</v>
       </c>
       <c r="B32">
-        <v>-19.485804753171056</v>
+        <v>-18.872814947338835</v>
       </c>
       <c r="C32">
         <v>592.998505179033</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-42.230142692941378</v>
+        <v>-43.074114061193214</v>
       </c>
       <c r="B33">
-        <v>-22.064835453592558</v>
+        <v>-21.55641625316013</v>
       </c>
       <c r="C33">
         <v>592.998505179033</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-44.385567001398691</v>
+        <v>-45.11212031243096</v>
       </c>
       <c r="B34">
-        <v>-24.671837648215149</v>
+        <v>-24.273354274970341</v>
       </c>
       <c r="C34">
         <v>592.998505179033</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-46.5154057074416</v>
+        <v>-47.118597968796529</v>
       </c>
       <c r="B35">
-        <v>-27.308765929123709</v>
+        <v>-27.025320660826267</v>
       </c>
       <c r="C35">
         <v>592.998505179033</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-48.617318909158392</v>
+        <v>-49.091445601877126</v>
       </c>
       <c r="B36">
-        <v>-29.978357152202058</v>
+        <v>-29.814650104035842</v>
       </c>
       <c r="C36">
         <v>592.998505179033</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-50.688966704637451</v>
+        <v>-51.028561783260074</v>
       </c>
       <c r="B37">
-        <v>-32.683348173334075</v>
+        <v>-32.643677297907068</v>
       </c>
       <c r="C37">
         <v>592.998505179033</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-52.726373577903757</v>
+        <v>-52.926436857853027</v>
       </c>
       <c r="B38">
-        <v>-35.428388937132027</v>
+        <v>-35.516301479838468</v>
       </c>
       <c r="C38">
         <v>592.998505179033</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-54.719021556729047</v>
+        <v>-54.775928263845266</v>
       </c>
       <c r="B39">
-        <v>-38.225781743121971</v>
+        <v>-38.442680063590885</v>
       </c>
       <c r="C39">
         <v>592.998505179033</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-56.654757054821715</v>
+        <v>-56.566485212746564</v>
       </c>
       <c r="B40">
-        <v>-41.089741979558418</v>
+        <v>-41.434535007015747</v>
       </c>
       <c r="C40">
         <v>592.998505179033</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-58.52142648589016</v>
+        <v>-58.287556916066627</v>
       </c>
       <c r="B41">
-        <v>-44.034485034695813</v>
+        <v>-44.503588267964432</v>
       </c>
       <c r="C41">
         <v>592.998505179033</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-58.52142648589016</v>
+        <v>-58.287556916066627</v>
       </c>
       <c r="B42">
-        <v>-44.034485034695813</v>
+        <v>-44.503588267964432</v>
       </c>
       <c r="C42">
         <v>592.998505179033</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-56.084507144817259</v>
+        <v>-56.077261071417446</v>
       </c>
       <c r="B43">
-        <v>-41.756732255376541</v>
+        <v>-41.978064504346456</v>
       </c>
       <c r="C43">
         <v>592.998505179033</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-53.67645764878614</v>
+        <v>-53.881500358297487</v>
       </c>
       <c r="B44">
-        <v>-39.445211989961329</v>
+        <v>-39.436392165737331</v>
       </c>
       <c r="C44">
         <v>592.998505179033</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-51.285296307579692</v>
+        <v>-51.690119626066533</v>
       </c>
       <c r="B45">
-        <v>-37.113938569224324</v>
+        <v>-36.88985365514322</v>
       </c>
       <c r="C45">
         <v>592.998505179033</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-48.899041430980745</v>
+        <v>-49.492963724084319</v>
       </c>
       <c r="B46">
-        <v>-34.776926323939634</v>
+        <v>-34.349731375570265</v>
       </c>
       <c r="C46">
         <v>592.998505179033</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-46.50734054828186</v>
+        <v>-47.281270214361889</v>
       </c>
       <c r="B47">
-        <v>-32.446283975514163</v>
+        <v>-31.825760422066313</v>
       </c>
       <c r="C47">
         <v>592.998505179033</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-44.10635806681443</v>
+        <v>-45.051847509515326</v>
       </c>
       <c r="B48">
-        <v>-30.126497807886047</v>
+        <v>-29.321486657846062</v>
       </c>
       <c r="C48">
         <v>592.998505179033</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-41.693887613419484</v>
+        <v>-42.802896734811924</v>
       </c>
       <c r="B49">
-        <v>-27.82014849562621</v>
+        <v>-26.838908638165872</v>
       </c>
       <c r="C49">
         <v>592.998505179033</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-39.267722814938118</v>
+        <v>-40.53261901551906</v>
       </c>
       <c r="B50">
-        <v>-25.529816713305589</v>
+        <v>-24.380024918282146</v>
       </c>
       <c r="C50">
         <v>592.998505179033</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-36.826319309227209</v>
+        <v>-38.239778401934089</v>
       </c>
       <c r="B51">
-        <v>-23.257308817249289</v>
+        <v>-21.946208642044173</v>
       </c>
       <c r="C51">
         <v>592.998505179033</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-34.370780778206672</v>
+        <v>-35.92539064447454</v>
       </c>
       <c r="B52">
-        <v>-21.001333890799046</v>
+        <v>-19.536331307672903</v>
       </c>
       <c r="C52">
         <v>592.998505179033</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-31.90287291481221</v>
+        <v>-33.591034418587952</v>
       </c>
       <c r="B53">
-        <v>-18.759826699050787</v>
+        <v>-17.148639001982204</v>
       </c>
       <c r="C53">
         <v>592.998505179033</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-29.42436141197954</v>
+        <v>-31.238288399721892</v>
       </c>
       <c r="B54">
-        <v>-16.530722007100405</v>
+        <v>-14.781377811785918</v>
       </c>
       <c r="C54">
         <v>592.998505179033</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-26.936596453698044</v>
+        <v>-28.868370385346758</v>
       </c>
       <c r="B55">
-        <v>-14.312440578238341</v>
+        <v>-12.4331947604195</v>
       </c>
       <c r="C55">
         <v>592.998505179033</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-24.439266188171938</v>
+        <v>-26.481054661024494</v>
       </c>
       <c r="B56">
-        <v>-12.105347168533216</v>
+        <v>-10.1043406173048</v>
       </c>
       <c r="C56">
         <v>592.998505179033</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-21.931643254659132</v>
+        <v>-24.075754634339877</v>
       </c>
       <c r="B57">
-        <v>-9.9102925322481639</v>
+        <v>-7.7954670883852621</v>
       </c>
       <c r="C57">
         <v>592.998505179033</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-19.413000292417522</v>
+        <v>-21.6518837128777</v>
       </c>
       <c r="B58">
-        <v>-7.7281274236463275</v>
+        <v>-5.5072258796043183</v>
       </c>
       <c r="C58">
         <v>592.998505179033</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-16.882697681381792</v>
+        <v>-19.208926421104223</v>
       </c>
       <c r="B59">
-        <v>-5.5595999714976987</v>
+        <v>-3.2401896858354648</v>
       </c>
       <c r="C59">
         <v>592.998505179033</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-14.340446764193903</v>
+        <v>-16.746651751011651</v>
       </c>
       <c r="B60">
-        <v>-3.4050478025997633</v>
+        <v>-0.99461515767247566</v>
       </c>
       <c r="C60">
         <v>592.998505179033</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-11.786046624172593</v>
+        <v>-14.264899811473692</v>
       </c>
       <c r="B61">
-        <v>-1.2647059182568652</v>
+        <v>1.2293200653608105</v>
       </c>
       <c r="C61">
         <v>592.998505179033</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-9.2192963446365859</v>
+        <v>-11.763510711364004</v>
       </c>
       <c r="B62">
-        <v>0.86119068022667133</v>
+        <v>3.431438343740576</v>
       </c>
       <c r="C62">
         <v>592.998505179033</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-6.6405445585594656</v>
+        <v>-9.2427917812990348</v>
       </c>
       <c r="B63">
-        <v>2.9730497698607303</v>
+        <v>5.6120811227090721</v>
       </c>
       <c r="C63">
         <v>592.998505179033</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.0523380975340668</v>
+        <v>-6.7049192388661183</v>
       </c>
       <c r="B64">
-        <v>5.0738502409121713</v>
+        <v>7.77366618657296</v>
       </c>
       <c r="C64">
         <v>592.998505179033</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4577733428080866</v>
+        <v>-4.15253652339537</v>
       </c>
       <c r="B65">
-        <v>7.1672137619620564</v>
+        <v>9.9191304044049726</v>
       </c>
       <c r="C65">
         <v>592.998505179033</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1.1400533243708177</v>
+        <v>-1.58828707421686</v>
       </c>
       <c r="B66">
-        <v>9.2567620015914827</v>
+        <v>12.051410645277864</v>
       </c>
       <c r="C66">
         <v>592.998505179033</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3.7420598346025353</v>
+        <v>0.98863304789527284</v>
       </c>
       <c r="B67">
-        <v>11.341421306349076</v>
+        <v>14.16961373028566</v>
       </c>
       <c r="C67">
         <v>592.998505179033</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6.36522136587731</v>
+        <v>3.5928172963907938</v>
       </c>
       <c r="B68">
-        <v>13.40133673465373</v>
+        <v>16.257526288607529</v>
       </c>
       <c r="C68">
         <v>592.998505179033</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>9.0226937341188567</v>
+        <v>6.2355874925393673</v>
       </c>
       <c r="B69">
-        <v>15.421120644810792</v>
+        <v>18.302569742647453</v>
       </c>
       <c r="C69">
         <v>592.998505179033</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>11.696298059594326</v>
+        <v>8.9013894146662409</v>
       </c>
       <c r="B70">
-        <v>17.422035882801172</v>
+        <v>20.322024879623452</v>
       </c>
       <c r="C70">
         <v>592.998505179033</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>14.366214338695661</v>
+        <v>11.573264857113385</v>
       </c>
       <c r="B71">
-        <v>19.427264827861336</v>
+        <v>22.334732317195815</v>
       </c>
       <c r="C71">
         <v>592.998505179033</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>17.037392767970221</v>
+        <v>14.255515721233756</v>
       </c>
       <c r="B72">
-        <v>21.431017504574225</v>
+        <v>24.335912629979674</v>
       </c>
       <c r="C72">
         <v>592.998505179033</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>19.718081564562866</v>
+        <v>16.955277967378738</v>
       </c>
       <c r="B73">
-        <v>23.423646422371366</v>
+        <v>26.317637744490721</v>
       </c>
       <c r="C73">
         <v>592.998505179033</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>22.40495082785284</v>
+        <v>19.669763684882298</v>
       </c>
       <c r="B74">
-        <v>25.409046384731926</v>
+        <v>28.283005037891897</v>
       </c>
       <c r="C74">
         <v>592.998505179033</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>25.091714290312609</v>
+        <v>22.393653368982836</v>
       </c>
       <c r="B75">
-        <v>27.394570096563875</v>
+        <v>30.237924496025816</v>
       </c>
       <c r="C75">
         <v>592.998505179033</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>27.771838334553127</v>
+        <v>25.121425009553931</v>
       </c>
       <c r="B76">
-        <v>29.387859574442654</v>
+        <v>32.188531088806521</v>
       </c>
       <c r="C76">
         <v>592.998505179033</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>30.439280707243139</v>
+        <v>27.847983254304236</v>
       </c>
       <c r="B77">
-        <v>31.395982113154808</v>
+        <v>34.140485768005732</v>
       </c>
       <c r="C77">
         <v>592.998505179033</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>33.090211961143893</v>
+        <v>30.570141887647733</v>
       </c>
       <c r="B78">
-        <v>33.423416808663646</v>
+        <v>36.097328428754466</v>
       </c>
       <c r="C78">
         <v>592.998505179033</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>35.718063902825079</v>
+        <v>33.282370062375527</v>
       </c>
       <c r="B79">
-        <v>35.47784611925784</v>
+        <v>38.065203858992028</v>
       </c>
       <c r="C79">
         <v>592.998505179033</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>38.311270861428845</v>
+        <v>35.974859739530658</v>
       </c>
       <c r="B80">
-        <v>37.572797780514627</v>
+        <v>40.055008819596964</v>
       </c>
       <c r="C80">
         <v>592.998505179033</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>40.84133296045632</v>
+        <v>38.623283011658309</v>
       </c>
       <c r="B81">
-        <v>39.741606546466024</v>
+        <v>42.093771689165045</v>
       </c>
       <c r="C81">
         <v>592.998505179033</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>42.793815026186707</v>
+        <v>40.786431333828588</v>
       </c>
       <c r="B82">
-        <v>42.585979234405343</v>
+        <v>44.671676492532484</v>
       </c>
       <c r="C82">
         <v>592.998505179033</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>56.565909492118593</v>
+        <v>42.516758566528168</v>
       </c>
       <c r="B1">
-        <v>31.189191715453795</v>
+        <v>49.069752159617025</v>
       </c>
       <c r="C1">
         <v>767.45943045334911</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>52.320673092227672</v>
+        <v>38.043646117870786</v>
       </c>
       <c r="B2">
-        <v>31.612328717593293</v>
+        <v>48.6178624757326</v>
       </c>
       <c r="C2">
         <v>767.45943045334911</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>48.685722474614842</v>
+        <v>34.389459277397009</v>
       </c>
       <c r="B3">
-        <v>30.857850988729943</v>
+        <v>47.291106030678328</v>
       </c>
       <c r="C3">
         <v>767.45943045334911</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>45.140017947845621</v>
+        <v>30.876795917664804</v>
       </c>
       <c r="B4">
-        <v>29.931162937565542</v>
+        <v>45.813158576344854</v>
       </c>
       <c r="C4">
         <v>767.45943045334911</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>41.654610541357776</v>
+        <v>27.46777655499065</v>
       </c>
       <c r="B5">
-        <v>28.888124843286334</v>
+        <v>44.224487159889847</v>
       </c>
       <c r="C5">
         <v>767.45943045334911</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>38.217705097383934</v>
+        <v>24.146831232521823</v>
       </c>
       <c r="B6">
-        <v>27.751496783129479</v>
+        <v>42.541725328472126</v>
       </c>
       <c r="C6">
         <v>767.45943045334911</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>34.822573932072615</v>
+        <v>20.904996785092319</v>
       </c>
       <c r="B7">
-        <v>26.534260576169025</v>
+        <v>40.77444852484286</v>
       </c>
       <c r="C7">
         <v>767.45943045334911</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>31.46526611929465</v>
+        <v>17.736929016536294</v>
       </c>
       <c r="B8">
-        <v>25.244039976629537</v>
+        <v>38.928366009457385</v>
       </c>
       <c r="C8">
         <v>767.45943045334911</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>28.139597260328319</v>
+        <v>14.634403682870142</v>
       </c>
       <c r="B9">
-        <v>23.892768474113044</v>
+        <v>37.012263827867464</v>
       </c>
       <c r="C9">
         <v>767.45943045334911</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>24.838888922434659</v>
+        <v>11.588565234548694</v>
       </c>
       <c r="B10">
-        <v>22.493332852159011</v>
+        <v>35.035602455935056</v>
       </c>
       <c r="C10">
         <v>767.45943045334911</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>21.556720009398177</v>
+        <v>8.5909129475981754</v>
       </c>
       <c r="B11">
-        <v>21.058123334679102</v>
+        <v>33.00746330566659</v>
       </c>
       <c r="C11">
         <v>767.45943045334911</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>18.2896665738427</v>
+        <v>5.6368510070882882</v>
       </c>
       <c r="B12">
-        <v>19.593746811405083</v>
+        <v>30.93275613404467</v>
       </c>
       <c r="C12">
         <v>767.45943045334911</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>15.046035927225709</v>
+        <v>2.7370484086912947</v>
       </c>
       <c r="B13">
-        <v>18.084173394976879</v>
+        <v>28.800083141811989</v>
       </c>
       <c r="C13">
         <v>767.45943045334911</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>11.830799035425244</v>
+        <v>-0.10215182129041413</v>
       </c>
       <c r="B14">
-        <v>16.519811050293463</v>
+        <v>26.602668007869667</v>
       </c>
       <c r="C14">
         <v>767.45943045334911</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>8.6238502231677234</v>
+        <v>-2.9069753446365616</v>
       </c>
       <c r="B15">
-        <v>14.939455928381848</v>
+        <v>24.368527879992097</v>
       </c>
       <c r="C15">
         <v>767.45943045334911</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>5.4067486601866221</v>
+        <v>-5.7014758637524041</v>
       </c>
       <c r="B16">
-        <v>13.378691675468819</v>
+        <v>22.123359579120248</v>
       </c>
       <c r="C16">
         <v>767.45943045334911</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2.1927895373950221</v>
+        <v>-8.4684505554634875</v>
       </c>
       <c r="B17">
-        <v>11.811863732452029</v>
+        <v>19.848785149987812</v>
       </c>
       <c r="C17">
         <v>767.45943045334911</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.0008604142226971</v>
+        <v>-11.185654552985083</v>
       </c>
       <c r="B18">
-        <v>10.205846970289633</v>
+        <v>17.521040169596972</v>
       </c>
       <c r="C18">
         <v>767.45943045334911</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.1732843245766933</v>
+        <v>-13.851931340671117</v>
       </c>
       <c r="B19">
-        <v>8.5588721855108361</v>
+        <v>15.138889120231129</v>
       </c>
       <c r="C19">
         <v>767.45943045334911</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-7.3276277888008021</v>
+        <v>-16.471396490660219</v>
       </c>
       <c r="B20">
-        <v>6.87700915603758</v>
+        <v>12.706728710493936</v>
       </c>
       <c r="C20">
         <v>767.45943045334911</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-10.467036402028837</v>
+        <v>-19.048165575091005</v>
       </c>
       <c r="B21">
-        <v>5.16632765979182</v>
+        <v>10.228955648989075</v>
       </c>
       <c r="C21">
         <v>767.45943045334911</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-13.594095975857577</v>
+        <v>-21.585617647573919</v>
       </c>
       <c r="B22">
-        <v>3.4318173096998206</v>
+        <v>7.7091798139013976</v>
       </c>
       <c r="C22">
         <v>767.45943045334911</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-16.709153187735669</v>
+        <v>-24.084185687606766</v>
       </c>
       <c r="B23">
-        <v>1.6741470587050806</v>
+        <v>5.147863761740437</v>
       </c>
       <c r="C23">
         <v>767.45943045334911</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-19.811994931574738</v>
+        <v>-26.543566156159187</v>
       </c>
       <c r="B24">
-        <v>-0.10709430524459551</v>
+        <v>2.5446832185968931</v>
       </c>
       <c r="C24">
         <v>767.45943045334911</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-22.902408101286372</v>
+        <v>-28.963455514200788</v>
       </c>
       <c r="B25">
-        <v>-1.9123179942013777</v>
+        <v>-0.10068608943851302</v>
       </c>
       <c r="C25">
         <v>767.45943045334911</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-25.980087560012134</v>
+        <v>-31.343421777903931</v>
       </c>
       <c r="B26">
-        <v>-3.7421128038899889</v>
+        <v>-2.7887056551905136</v>
       </c>
       <c r="C26">
         <v>767.45943045334911</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-29.044360047813448</v>
+        <v>-33.682519184251859</v>
       </c>
       <c r="B27">
-        <v>-5.5977778647252663</v>
+        <v>-5.5203858471456568</v>
       </c>
       <c r="C27">
         <v>767.45943045334911</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-32.09446027398166</v>
+        <v>-35.97967352543052</v>
       </c>
       <c r="B28">
-        <v>-7.4807898907945605</v>
+        <v>-8.2968742527059014</v>
       </c>
       <c r="C28">
         <v>767.45943045334911</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-35.129622947808137</v>
+        <v>-38.233810593625854</v>
       </c>
       <c r="B29">
-        <v>-9.3926255961852316</v>
+        <v>-11.119318459273231</v>
       </c>
       <c r="C29">
         <v>767.45943045334911</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-38.149500271522157</v>
+        <v>-40.4443894032176</v>
       </c>
       <c r="B30">
-        <v>-11.33395609562754</v>
+        <v>-13.988296407423306</v>
       </c>
       <c r="C30">
         <v>767.45943045334911</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-41.155414419104908</v>
+        <v>-42.613001857360658</v>
       </c>
       <c r="B31">
-        <v>-13.302230106423451</v>
+        <v>-16.902107450426662</v>
       </c>
       <c r="C31">
         <v>767.45943045334911</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-44.149105057475559</v>
+        <v>-44.741773081403743</v>
       </c>
       <c r="B32">
-        <v>-15.294090746517863</v>
+        <v>-19.858481294727579</v>
       </c>
       <c r="C32">
         <v>767.45943045334911</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-47.132311853553247</v>
+        <v>-46.832828200695545</v>
       </c>
       <c r="B33">
-        <v>-17.306181133855649</v>
+        <v>-22.855147646770309</v>
       </c>
       <c r="C33">
         <v>767.45943045334911</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-50.106100549190451</v>
+        <v>-48.887405973730033</v>
       </c>
       <c r="B34">
-        <v>-19.336444800235586</v>
+        <v>-25.890783127946758</v>
       </c>
       <c r="C34">
         <v>767.45943045334911</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-53.068841185972914</v>
+        <v>-50.9031996915822</v>
       </c>
       <c r="B35">
-        <v>-21.388026932871991</v>
+        <v>-28.967852019439473</v>
       </c>
       <c r="C35">
         <v>767.45943045334911</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-56.018229880419767</v>
+        <v>-52.877016278472311</v>
       </c>
       <c r="B36">
-        <v>-23.465373132833069</v>
+        <v>-32.0897655173787</v>
       </c>
       <c r="C36">
         <v>767.45943045334911</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-58.951962749050139</v>
+        <v>-54.805662658620655</v>
       </c>
       <c r="B37">
-        <v>-25.572929001187056</v>
+        <v>-35.259934817894695</v>
       </c>
       <c r="C37">
         <v>767.45943045334911</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-61.866082746469985</v>
+        <v>-56.68378690521849</v>
       </c>
       <c r="B38">
-        <v>-27.71833009996498</v>
+        <v>-38.484077440169131</v>
       </c>
       <c r="C38">
         <v>767.45943045334911</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-64.7500201796328</v>
+        <v>-58.497401687341075</v>
       </c>
       <c r="B39">
-        <v>-29.921971835049149</v>
+        <v>-41.777136195589577</v>
       </c>
       <c r="C39">
         <v>767.45943045334911</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-67.59155219357892</v>
+        <v>-60.230360823034694</v>
       </c>
       <c r="B40">
-        <v>-32.207439573284709</v>
+        <v>-45.156360218595061</v>
       </c>
       <c r="C40">
         <v>767.45943045334911</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-70.378455933348675</v>
+        <v>-61.866518130345611</v>
       </c>
       <c r="B41">
-        <v>-34.59831868151678</v>
+        <v>-48.6389986436246</v>
       </c>
       <c r="C41">
         <v>767.45943045334911</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-70.378455933348675</v>
+        <v>-61.866518130345611</v>
       </c>
       <c r="B42">
-        <v>-34.59831868151678</v>
+        <v>-48.6389986436246</v>
       </c>
       <c r="C42">
         <v>767.45943045334911</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-67.014085545255213</v>
+        <v>-59.479905281617285</v>
       </c>
       <c r="B43">
-        <v>-33.321726111618254</v>
+        <v>-45.958079693918421</v>
       </c>
       <c r="C43">
         <v>767.45943045334911</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-63.69426221278222</v>
+        <v>-57.125375408561958</v>
       </c>
       <c r="B44">
-        <v>-31.959175011397043</v>
+        <v>-43.242886166967082</v>
       </c>
       <c r="C44">
         <v>767.45943045334911</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-60.406768072903475</v>
+        <v>-54.7873123873761</v>
       </c>
       <c r="B45">
-        <v>-30.534241115203898</v>
+        <v>-40.510100930564079</v>
       </c>
       <c r="C45">
         <v>767.45943045334911</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-57.1393852625928</v>
+        <v>-52.450100094256108</v>
       </c>
       <c r="B46">
-        <v>-29.070500157389532</v>
+        <v>-37.77640685250293</v>
       </c>
       <c r="C46">
         <v>767.45943045334911</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-53.881548908245023</v>
+        <v>-50.100260113481</v>
       </c>
       <c r="B47">
-        <v>-27.588338244184712</v>
+        <v>-35.056203064755707</v>
       </c>
       <c r="C47">
         <v>767.45943045334911</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-50.629306093938986</v>
+        <v>-47.732864861659884</v>
       </c>
       <c r="B48">
-        <v>-26.09538296934037</v>
+        <v>-32.3547537560088</v>
       </c>
       <c r="C48">
         <v>767.45943045334911</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-47.3803568931745</v>
+        <v>-45.345124463484396</v>
       </c>
       <c r="B49">
-        <v>-24.596072298487464</v>
+        <v>-29.67503937912711</v>
       </c>
       <c r="C49">
         <v>767.45943045334911</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-44.132401379451387</v>
+        <v>-42.934249043646204</v>
       </c>
       <c r="B50">
-        <v>-23.094844197256958</v>
+        <v>-27.020040386975573</v>
       </c>
       <c r="C50">
         <v>767.45943045334911</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-40.88381335835593</v>
+        <v>-40.498313728275811</v>
       </c>
       <c r="B51">
-        <v>-21.594836589802952</v>
+        <v>-24.391813142367941</v>
       </c>
       <c r="C51">
         <v>767.45943045334911</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-37.635661563820037</v>
+        <v>-38.038853649258975</v>
       </c>
       <c r="B52">
-        <v>-20.093987234371991</v>
+        <v>-21.788717647913156</v>
       </c>
       <c r="C52">
         <v>767.45943045334911</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-34.389688461862065</v>
+        <v>-35.558268939920367</v>
       </c>
       <c r="B53">
-        <v>-18.58893384773376</v>
+        <v>-19.208189816168957</v>
       </c>
       <c r="C53">
         <v>767.45943045334911</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-31.147636518500303</v>
+        <v>-33.058959733584572</v>
       </c>
       <c r="B54">
-        <v>-17.076314146657914</v>
+        <v>-16.64766555969306</v>
       </c>
       <c r="C54">
         <v>767.45943045334911</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-27.910830520237</v>
+        <v>-30.542774024740083</v>
       </c>
       <c r="B55">
-        <v>-15.553571807294564</v>
+        <v>-14.105170646715644</v>
       </c>
       <c r="C55">
         <v>767.45943045334911</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-24.678924535510113</v>
+        <v>-28.009351252530791</v>
       </c>
       <c r="B56">
-        <v>-14.021374343315612</v>
+        <v>-11.581090268156684</v>
       </c>
       <c r="C56">
         <v>767.45943045334911</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-21.451154953241456</v>
+        <v>-25.45777871726445</v>
       </c>
       <c r="B57">
-        <v>-12.481195227773373</v>
+        <v>-9.07639947060857</v>
       </c>
       <c r="C57">
         <v>767.45943045334911</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-18.226758162352876</v>
+        <v>-22.887143719248797</v>
       </c>
       <c r="B58">
-        <v>-10.934507933720187</v>
+        <v>-6.5920733006636993</v>
       </c>
       <c r="C58">
         <v>767.45943045334911</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-15.005062397123332</v>
+        <v>-20.296644073004273</v>
       </c>
       <c r="B59">
-        <v>-9.3826087083107765</v>
+        <v>-4.128968741429361</v>
       </c>
       <c r="C59">
         <v>767.45943045334911</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-11.785763273260375</v>
+        <v>-17.685919649902136</v>
       </c>
       <c r="B60">
-        <v>-7.8260848951095445</v>
+        <v>-1.6874705220725033</v>
       </c>
       <c r="C60">
         <v>767.45943045334911</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-8.56864825182874</v>
+        <v>-15.054720835526371</v>
       </c>
       <c r="B61">
-        <v>-6.2653466117833148</v>
+        <v>0.73215469172499725</v>
       </c>
       <c r="C61">
         <v>767.45943045334911</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-5.3535047938931086</v>
+        <v>-12.402798015460936</v>
       </c>
       <c r="B62">
-        <v>-4.7008039759989</v>
+        <v>3.1296402342812968</v>
       </c>
       <c r="C62">
         <v>767.45943045334911</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.140679951337606</v>
+        <v>-9.7306197566844</v>
       </c>
       <c r="B63">
-        <v>-3.1317873122976367</v>
+        <v>5.50548668058249</v>
       </c>
       <c r="C63">
         <v>767.45943045334911</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1.0672408606759898</v>
+        <v>-7.04152735175376</v>
       </c>
       <c r="B64">
-        <v>-1.5533077727189759</v>
+        <v>7.8632635682865173</v>
       </c>
       <c r="C64">
         <v>767.45943045334911</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4.2671126361664733</v>
+        <v>-4.3395802746206229</v>
       </c>
       <c r="B65">
-        <v>0.04070328382310652</v>
+        <v>10.207307675719266</v>
       </c>
       <c r="C65">
         <v>767.45943045334911</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>7.455790369152667</v>
+        <v>-1.6288379992365729</v>
       </c>
       <c r="B66">
-        <v>1.6563144984146456</v>
+        <v>12.541955781206646</v>
       </c>
       <c r="C66">
         <v>767.45943045334911</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>10.634191673727298</v>
+        <v>1.0919269904958773</v>
       </c>
       <c r="B67">
-        <v>3.2917552319479046</v>
+        <v>14.865896516509849</v>
       </c>
       <c r="C67">
         <v>767.45943045334911</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>13.819484644278871</v>
+        <v>3.8450901708706482</v>
       </c>
       <c r="B68">
-        <v>4.9138977245401456</v>
+        <v>17.15522592713133</v>
       </c>
       <c r="C68">
         <v>767.45943045334911</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>17.024966058479489</v>
+        <v>6.64800671481553</v>
       </c>
       <c r="B69">
-        <v>6.4970843552599868</v>
+        <v>19.391403300975725</v>
       </c>
       <c r="C69">
         <v>767.45943045334911</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>20.232196946839689</v>
+        <v>9.4768026215972938</v>
       </c>
       <c r="B70">
-        <v>8.076895179756443</v>
+        <v>21.599933481815032</v>
       </c>
       <c r="C70">
         <v>767.45943045334911</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>23.421073663700906</v>
+        <v>12.30544892011293</v>
       </c>
       <c r="B71">
-        <v>9.6921224326872988</v>
+        <v>23.808623490724123</v>
       </c>
       <c r="C71">
         <v>767.45943045334911</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>26.596569605889297</v>
+        <v>15.140525931441067</v>
       </c>
       <c r="B72">
-        <v>11.333169388164905</v>
+        <v>26.010443502121749</v>
       </c>
       <c r="C72">
         <v>767.45943045334911</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>29.766994708501095</v>
+        <v>17.992959854706463</v>
       </c>
       <c r="B73">
-        <v>12.984001096224596</v>
+        <v>28.19372094362204</v>
       </c>
       <c r="C73">
         <v>767.45943045334911</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>32.928928017227776</v>
+        <v>20.858451109036633</v>
       </c>
       <c r="B74">
-        <v>14.651218671139027</v>
+        <v>30.363049102276605</v>
       </c>
       <c r="C74">
         <v>767.45943045334911</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>36.075951615123152</v>
+        <v>23.728815284118411</v>
       </c>
       <c r="B75">
-        <v>16.347206202063919</v>
+        <v>32.52717146891198</v>
       </c>
       <c r="C75">
         <v>767.45943045334911</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>39.201390624094969</v>
+        <v>26.595554431873111</v>
       </c>
       <c r="B76">
-        <v>18.084843613449927</v>
+        <v>34.695166490016931</v>
       </c>
       <c r="C76">
         <v>767.45943045334911</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>42.299064391513767</v>
+        <v>29.450823606256879</v>
       </c>
       <c r="B77">
-        <v>19.876057166394826</v>
+        <v>36.875415003201582</v>
       </c>
       <c r="C77">
         <v>767.45943045334911</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>45.365026127746923</v>
+        <v>32.289703407130624</v>
       </c>
       <c r="B78">
-        <v>21.728462633289979</v>
+        <v>39.073172454899122</v>
       </c>
       <c r="C78">
         <v>767.45943045334911</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>48.392552461871844</v>
+        <v>35.103676477413032</v>
       </c>
       <c r="B79">
-        <v>23.655033510930441</v>
+        <v>41.2975380264381</v>
       </c>
       <c r="C79">
         <v>767.45943045334911</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>51.369852898811239</v>
+        <v>37.87766168107273</v>
       </c>
       <c r="B80">
-        <v>25.678520879370879</v>
+        <v>43.564623052599934</v>
       </c>
       <c r="C80">
         <v>767.45943045334911</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>54.267983399978007</v>
+        <v>40.574302763674744</v>
       </c>
       <c r="B81">
-        <v>27.854775500999462</v>
+        <v>45.914335609283569</v>
       </c>
       <c r="C81">
         <v>767.45943045334911</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>56.565909492118593</v>
+        <v>42.516758566528168</v>
       </c>
       <c r="B82">
-        <v>31.189191715453795</v>
+        <v>49.069752159617025</v>
       </c>
       <c r="C82">
         <v>767.45943045334911</v>
